--- a/صلاحيات_النظام.xlsx
+++ b/صلاحيات_النظام.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="كل الصلاحيات" sheetId="1" r:id="R24474ab6616c4a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ملخص حسب الوحدة" sheetId="2" r:id="R70752f606bd04683"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اختبار الأدوار" sheetId="3" r:id="R4bd5fd001a834cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اعتماد الزبائن" sheetId="4" r:id="R18125932f0264fc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="كل الصلاحيات" sheetId="1" r:id="R6f4a725ec7164782"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ملخص حسب الوحدة" sheetId="2" r:id="R5c35446b3b384fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اختبار الأدوار" sheetId="3" r:id="R259782c88b2d473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اعتماد الزبائن" sheetId="4" r:id="Rf2b5f743aac248ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -117,7 +117,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="50">
+  <x:fills count="51">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -364,6 +364,11 @@
         <x:fgColor rgb="FFC6EFCE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -413,7 +418,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="145">
+  <x:cellXfs count="146">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -735,6 +740,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="14" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -12943,6 +12949,46 @@
         <x:v>إضافة 2026-09-02: تصدير Excel مستقل لنفس لقطة التوليد ولا يُمنح تلقائياً.</x:v>
       </x:c>
     </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="145" t="n">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B224" s="145"/>
+      <x:c r="C224" s="145" t="str">
+        <x:v>الأسماء المقترحة</x:v>
+      </x:c>
+      <x:c r="D224" s="145" t="str">
+        <x:v>candidates</x:v>
+      </x:c>
+      <x:c r="E224" s="145" t="str">
+        <x:v>candidates</x:v>
+      </x:c>
+      <x:c r="F224" s="145" t="str">
+        <x:v>link_restricted_lead</x:v>
+      </x:c>
+      <x:c r="G224" s="145" t="str">
+        <x:v>ربط زبون Lead مقيّد ضمن الفرع</x:v>
+      </x:c>
+      <x:c r="H224" s="145" t="str">
+        <x:v>candidates.link_restricted_lead</x:v>
+      </x:c>
+      <x:c r="I224" s="145" t="str">
+        <x:v>عام (كل الفروع) / الفرع / المُسند فقط</x:v>
+      </x:c>
+      <x:c r="J224" s="145" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K224" s="145" t="str">
+        <x:v>❌</x:v>
+      </x:c>
+      <x:c r="L224" s="145"/>
+      <x:c r="M224" s="145" t="str">
+        <x:v>تمت الإضافة</x:v>
+      </x:c>
+      <x:c r="N224" s="145" t="str">
+        <x:v>إضافة 2026-09-15: ربط تطابق هاتف محجوب لزبون Lead واحد داخل فرع الاسم نفسه، ثم إضافة مسؤول الاسم دون حذف المسؤول الحالي.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13046,7 +13092,7 @@
         </x:is>
       </x:c>
       <x:c r="C6" s="29" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -13372,7 +13418,7 @@
       </x:c>
       <x:c r="B30"/>
       <x:c r="C30" t="n">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22660,6 +22706,56 @@
         <x:v>اختبار إلزامي: فقد صلاحية العرض أو التصدير، الفرع الخاطئ، والنطاقات الثلاثة.</x:v>
       </x:c>
     </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="145" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B211" s="145"/>
+      <x:c r="C211" s="145" t="str">
+        <x:v>candidates.link_restricted_lead</x:v>
+      </x:c>
+      <x:c r="D211" s="145" t="str">
+        <x:v>الأسماء المقترحة</x:v>
+      </x:c>
+      <x:c r="E211" s="145" t="str">
+        <x:v>link_restricted_lead</x:v>
+      </x:c>
+      <x:c r="F211" s="145" t="str">
+        <x:v>مضاف</x:v>
+      </x:c>
+      <x:c r="G211" s="145" t="str">
+        <x:v>❌</x:v>
+      </x:c>
+      <x:c r="H211" s="145"/>
+      <x:c r="I211" s="145" t="str">
+        <x:v>✅</x:v>
+      </x:c>
+      <x:c r="J211" s="145" t="str">
+        <x:v>ASSIGNED</x:v>
+      </x:c>
+      <x:c r="K211" s="145" t="str">
+        <x:v>❌</x:v>
+      </x:c>
+      <x:c r="L211" s="145"/>
+      <x:c r="M211" s="145" t="str">
+        <x:v>لا يكشف هوية الزبون قبل النجاح؛ التطابق الدقيق وLead والفرع نفسه وإسناد الاسم شروط خادمية.</x:v>
+      </x:c>
+      <x:c r="N211" s="145" t="str">
+        <x:v>❌</x:v>
+      </x:c>
+      <x:c r="O211" s="145"/>
+      <x:c r="P211" s="145" t="str">
+        <x:v>❌</x:v>
+      </x:c>
+      <x:c r="Q211" s="145"/>
+      <x:c r="R211" s="145" t="str">
+        <x:v>❌</x:v>
+      </x:c>
+      <x:c r="S211" s="145"/>
+      <x:c r="T211" s="145" t="str">
+        <x:v>اختبار إلزامي: فقد الصلاحية، اسم غير مسند، فرع آخر، FOP/OP، عدم التطابق، تعدد المطابقات، وحالة النجاح داخل الفرع.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
